--- a/Employee_Reports_wi52/Sandy De Vera Apigo Q0090.xlsx
+++ b/Employee_Reports_wi52/Sandy De Vera Apigo Q0090.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-253</v>
+        <v>-261</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -628,11 +628,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-439</v>
+        <v>-447</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -665,11 +665,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-388</v>
+        <v>-396</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -702,11 +702,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
